--- a/results/feature_selection/induction/wnp/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/qP_calc/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,38 +496,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4137902550609165</v>
+        <v>0.9443233478494916</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003037562549005084</v>
+        <v>0.001307054044992643</v>
       </c>
       <c r="F2" t="n">
-        <v>2.794645013469066e-05</v>
+        <v>2.747238939585558e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005286440213857589</v>
+        <v>0.001657479695074892</v>
       </c>
       <c r="H2" t="n">
-        <v>686.4816928222339</v>
+        <v>488.0464454443877</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1773824859968194</v>
+        <v>0.01820491871241025</v>
       </c>
       <c r="J2" t="n">
-        <v>-560.2019002031659</v>
+        <v>-659.8555369763629</v>
       </c>
       <c r="K2" t="n">
-        <v>-554.2349480634731</v>
+        <v>-654.0018058206186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,32 +535,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.411573160137731</v>
+        <v>0.9439892465103388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003029461629521352</v>
+        <v>0.001315974746197147</v>
       </c>
       <c r="F3" t="n">
-        <v>2.805214597692051e-05</v>
+        <v>2.763724417308014e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005296427661822685</v>
+        <v>0.001662445312576631</v>
       </c>
       <c r="H3" t="n">
-        <v>691.0422324715469</v>
+        <v>505.0427035794352</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1780476884608646</v>
+        <v>0.01830516065399049</v>
       </c>
       <c r="J3" t="n">
-        <v>-559.9980528693185</v>
+        <v>-659.5444307892698</v>
       </c>
       <c r="K3" t="n">
-        <v>-554.0311007296257</v>
+        <v>-653.6906996335255</v>
       </c>
     </row>
     <row r="4">
@@ -570,81 +570,81 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3690538472068956</v>
+        <v>0.8632151894766347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002969614200188726</v>
+        <v>0.001997720160800145</v>
       </c>
       <c r="F4" t="n">
-        <v>3.007917447455557e-05</v>
+        <v>6.749338246807466e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005484448420265757</v>
+        <v>0.002597948853770502</v>
       </c>
       <c r="H4" t="n">
-        <v>732.143259352446</v>
+        <v>789.5093691324347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1908049012600635</v>
+        <v>0.04204016769378237</v>
       </c>
       <c r="J4" t="n">
-        <v>-556.2305851938153</v>
+        <v>-615.1154369605832</v>
       </c>
       <c r="K4" t="n">
-        <v>-550.2636330541225</v>
+        <v>-611.2129495234203</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FS_calc, V_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.03155311911089509</v>
+        <v>0.7799199476616367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003004413989698653</v>
+        <v>0.002362098736815447</v>
       </c>
       <c r="F5" t="n">
-        <v>4.917736024247253e-05</v>
+        <v>1.085935425814675e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007012657145652604</v>
+        <v>0.003295353434481156</v>
       </c>
       <c r="H5" t="n">
-        <v>352.8241192006004</v>
+        <v>998.6258502117435</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6210007197708767</v>
+        <v>0.06653161724948968</v>
       </c>
       <c r="J5" t="n">
-        <v>-531.6841686943958</v>
+        <v>-592.3851527017114</v>
       </c>
       <c r="K5" t="n">
-        <v>-527.7062006012673</v>
+        <v>-590.43390898313</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,110 +652,110 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.1702258548503062</v>
+        <v>0.7735594627749365</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003388336628126174</v>
+        <v>0.002436232789834401</v>
       </c>
       <c r="F6" t="n">
-        <v>5.57883228336613e-05</v>
+        <v>1.117319805227705e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007469158107421566</v>
+        <v>0.003342633400819935</v>
       </c>
       <c r="H6" t="n">
-        <v>520.0586303067519</v>
+        <v>1181.798859684656</v>
       </c>
       <c r="I6" t="n">
-        <v>0.703213616562151</v>
+        <v>0.06843998240615566</v>
       </c>
       <c r="J6" t="n">
-        <v>-526.873082849293</v>
+        <v>-590.9036192864149</v>
       </c>
       <c r="K6" t="n">
-        <v>-524.8840988027288</v>
+        <v>-588.9523755678335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T, FS_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.2359399751458631</v>
+        <v>0.7259091498201793</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006536594406568398</v>
+        <v>0.002901391630950066</v>
       </c>
       <c r="F7" t="n">
-        <v>5.892112026980027e-05</v>
+        <v>1.352439537065877e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00767600939745388</v>
+        <v>0.003677552905215473</v>
       </c>
       <c r="H7" t="n">
-        <v>3508.881859610045</v>
+        <v>1421.954792049511</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7436464746558957</v>
+        <v>0.08273672213070568</v>
       </c>
       <c r="J7" t="n">
-        <v>-521.9227914698827</v>
+        <v>-580.9728028177755</v>
       </c>
       <c r="K7" t="n">
-        <v>-517.9448233767541</v>
+        <v>-579.0215590991941</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.2869404275860004</v>
+        <v>0.09210216566345086</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004789609389857829</v>
+        <v>0.005823080321167763</v>
       </c>
       <c r="F8" t="n">
-        <v>6.135247118689066e-05</v>
+        <v>4.479817279444646e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007832781829394373</v>
+        <v>0.00669314371535876</v>
       </c>
       <c r="H8" t="n">
-        <v>1620.364034116287</v>
+        <v>3652.648808955834</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7732501500112621</v>
+        <v>0.2734007090219209</v>
       </c>
       <c r="J8" t="n">
-        <v>-521.7392558035776</v>
+        <v>-516.6938466710941</v>
       </c>
       <c r="K8" t="n">
-        <v>-519.7502717570134</v>
+        <v>-512.7913592339312</v>
       </c>
     </row>
     <row r="9">
@@ -765,42 +765,42 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.6841469515879244</v>
+        <v>0.08441259090444342</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007766534672190275</v>
+        <v>0.005872918194218104</v>
       </c>
       <c r="F9" t="n">
-        <v>8.02885472450379e-05</v>
+        <v>4.517759753337819e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008960387672697979</v>
+        <v>0.006721428236124982</v>
       </c>
       <c r="H9" t="n">
-        <v>4025.340033665543</v>
+        <v>3666.670602329388</v>
       </c>
       <c r="I9" t="n">
-        <v>1.011600574918898</v>
+        <v>0.2757078470469404</v>
       </c>
       <c r="J9" t="n">
-        <v>-507.2137128760233</v>
+        <v>-516.2552796367498</v>
       </c>
       <c r="K9" t="n">
-        <v>-505.224728829459</v>
+        <v>-512.3527921995869</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.7625826495865282</v>
+        <v>-0.352626988534577</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008526677139842384</v>
+        <v>0.007632830563190156</v>
       </c>
       <c r="F10" t="n">
-        <v>8.402782203844042e-05</v>
+        <v>6.674233076355335e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009166669080884312</v>
+        <v>0.008169597956053489</v>
       </c>
       <c r="H10" t="n">
-        <v>4348.425758412885</v>
+        <v>4279.789590851045</v>
       </c>
       <c r="I10" t="n">
-        <v>1.058667228702771</v>
+        <v>0.8126696323838152</v>
       </c>
       <c r="J10" t="n">
-        <v>-504.7555803577243</v>
+        <v>-497.9629004350699</v>
       </c>
       <c r="K10" t="n">
-        <v>-502.76659631116</v>
+        <v>-496.0116567164885</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/qP_calc/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,38 +496,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, Plag1, Xlag1_calc</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9443233478494916</v>
+        <v>0.4099626555624998</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001307054044992643</v>
+        <v>0.00308006200338032</v>
       </c>
       <c r="F2" t="n">
-        <v>2.747238939585558e-06</v>
+        <v>2.911406318157078e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001657479695074892</v>
+        <v>0.005395744914427551</v>
       </c>
       <c r="H2" t="n">
-        <v>488.0464454443877</v>
+        <v>681.7891899134486</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01820491871241025</v>
+        <v>0.1785315831754772</v>
       </c>
       <c r="J2" t="n">
-        <v>-659.8555369763629</v>
+        <v>-537.1030399433712</v>
       </c>
       <c r="K2" t="n">
-        <v>-654.0018058206186</v>
+        <v>-531.2493087876269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,32 +535,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Plag1, Xlag1_calc</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9439892465103388</v>
+        <v>0.4062135521981558</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001315974746197147</v>
+        <v>0.003072480243175468</v>
       </c>
       <c r="F3" t="n">
-        <v>2.763724417308014e-06</v>
+        <v>2.929905423892124e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001662445312576631</v>
+        <v>0.005412860079377744</v>
       </c>
       <c r="H3" t="n">
-        <v>505.0427035794352</v>
+        <v>686.6256939802971</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01830516065399049</v>
+        <v>0.1796564436785205</v>
       </c>
       <c r="J3" t="n">
-        <v>-659.5444307892698</v>
+        <v>-536.7736766918611</v>
       </c>
       <c r="K3" t="n">
-        <v>-653.6906996335255</v>
+        <v>-530.9199455361168</v>
       </c>
     </row>
     <row r="4">
@@ -570,75 +570,75 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8632151894766347</v>
+        <v>0.3494491874262817</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001997720160800145</v>
+        <v>0.003016813521224111</v>
       </c>
       <c r="F4" t="n">
-        <v>6.749338246807466e-06</v>
+        <v>3.209996390677554e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002597948853770502</v>
+        <v>0.005665683004437819</v>
       </c>
       <c r="H4" t="n">
-        <v>789.5093691324347</v>
+        <v>730.0081669513347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04204016769378237</v>
+        <v>0.1966877137468502</v>
       </c>
       <c r="J4" t="n">
-        <v>-615.1154369605832</v>
+        <v>-532.0260939158795</v>
       </c>
       <c r="K4" t="n">
-        <v>-611.2129495234203</v>
+        <v>-526.1723627601352</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7799199476616367</v>
+        <v>0.0286685014251129</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002362098736815447</v>
+        <v>0.005827959059884888</v>
       </c>
       <c r="F5" t="n">
-        <v>1.085935425814675e-05</v>
+        <v>4.792816401598898e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003295353434481156</v>
+        <v>0.00692301697354477</v>
       </c>
       <c r="H5" t="n">
-        <v>998.6258502117435</v>
+        <v>1384.410590448326</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06653161724948968</v>
+        <v>0.2924329992872773</v>
       </c>
       <c r="J5" t="n">
-        <v>-592.3851527017114</v>
+        <v>-513.1819770548879</v>
       </c>
       <c r="K5" t="n">
-        <v>-590.43390898313</v>
+        <v>-509.279489617725</v>
       </c>
     </row>
     <row r="6">
@@ -648,42 +648,42 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7735594627749365</v>
+        <v>-0.06767218388406326</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002436232789834401</v>
+        <v>0.003130601438736722</v>
       </c>
       <c r="F6" t="n">
-        <v>1.117319805227705e-05</v>
+        <v>5.268187804017697e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003342633400819935</v>
+        <v>0.007258228298984331</v>
       </c>
       <c r="H6" t="n">
-        <v>1181.798859684656</v>
+        <v>368.6735462690988</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06843998240615566</v>
+        <v>0.6426770649596943</v>
       </c>
       <c r="J6" t="n">
-        <v>-590.9036192864149</v>
+        <v>-508.2644296514807</v>
       </c>
       <c r="K6" t="n">
-        <v>-588.9523755678335</v>
+        <v>-504.3619422143178</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -691,116 +691,116 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7259091498201793</v>
+        <v>-0.2247372506506775</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002901391630950066</v>
+        <v>0.003499644741479858</v>
       </c>
       <c r="F7" t="n">
-        <v>1.352439537065877e-05</v>
+        <v>6.043189983213698e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003677552905215473</v>
+        <v>0.007773795715873744</v>
       </c>
       <c r="H7" t="n">
-        <v>1421.954792049511</v>
+        <v>492.3196195482726</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08273672213070568</v>
+        <v>0.7359269550501716</v>
       </c>
       <c r="J7" t="n">
-        <v>-580.9728028177755</v>
+        <v>-503.1276593753371</v>
       </c>
       <c r="K7" t="n">
-        <v>-579.0215590991941</v>
+        <v>-501.1764156567556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09210216566345086</v>
+        <v>-0.293664827423789</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005823080321167763</v>
+        <v>0.004898520494063741</v>
       </c>
       <c r="F8" t="n">
-        <v>4.479817279444646e-05</v>
+        <v>6.383297578782592e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00669314371535876</v>
+        <v>0.007989554167024961</v>
       </c>
       <c r="H8" t="n">
-        <v>3652.648808955834</v>
+        <v>1717.876784827925</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2734007090219209</v>
+        <v>0.7772882626203765</v>
       </c>
       <c r="J8" t="n">
-        <v>-516.6938466710941</v>
+        <v>-500.2805132416486</v>
       </c>
       <c r="K8" t="n">
-        <v>-512.7913592339312</v>
+        <v>-498.3292695230671</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08441259090444342</v>
+        <v>-0.3583422674677508</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005872918194218104</v>
+        <v>0.00687141251621259</v>
       </c>
       <c r="F9" t="n">
-        <v>4.517759753337819e-05</v>
+        <v>6.702433832379777e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006721428236124982</v>
+        <v>0.008186839336630333</v>
       </c>
       <c r="H9" t="n">
-        <v>3666.670602329388</v>
+        <v>3666.938734089613</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2757078470469404</v>
+        <v>0.8160991945543038</v>
       </c>
       <c r="J9" t="n">
-        <v>-516.2552796367498</v>
+        <v>-497.7436467905222</v>
       </c>
       <c r="K9" t="n">
-        <v>-512.3527921995869</v>
+        <v>-495.7924030719407</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.352626988534577</v>
+        <v>-0.710228874111982</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007632830563190156</v>
+        <v>0.008508530041582805</v>
       </c>
       <c r="F10" t="n">
-        <v>6.674233076355335e-05</v>
+        <v>8.43873899936127e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008169597956053489</v>
+        <v>0.009186260936507993</v>
       </c>
       <c r="H10" t="n">
-        <v>4279.789590851045</v>
+        <v>4416.195759698109</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8126696323838152</v>
+        <v>1.02725546681318</v>
       </c>
       <c r="J10" t="n">
-        <v>-497.9629004350699</v>
+        <v>-485.7648139095377</v>
       </c>
       <c r="K10" t="n">
-        <v>-496.0116567164885</v>
+        <v>-483.8135701909562</v>
       </c>
     </row>
   </sheetData>
